--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -37,13 +37,13 @@
     <t>url</t>
   </si>
   <si>
-    <t>index.report.json</t>
-  </si>
-  <si>
-    <t>["hero","hero","cards-service","cards-service","cards-service","columns","columns","columns","columns","columns","columns","columns","columns"]</t>
-  </si>
-  <si>
-    <t>index</t>
+    <t>en/index.report.json</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>en/index</t>
   </si>
   <si>
     <t>success</t>
@@ -52,13 +52,13 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-03-13T17:16:31.918Z</t>
-  </si>
-  <si>
-    <t>BT Wholesale | The UK's Largest Network Provider</t>
-  </si>
-  <si>
-    <t>https://www.btwholesale.com/</t>
+    <t>2026-04-01T18:37:00.339Z</t>
+  </si>
+  <si>
+    <t>Challenge Validation</t>
+  </si>
+  <si>
+    <t>https://www.directlinegroup.co.uk/en/index.html</t>
   </si>
 </sst>
 </file>
@@ -450,13 +450,13 @@
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="50" customWidth="1"/>
-    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="49" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
